--- a/data/trending_integrated_20261020_13.xlsx
+++ b/data/trending_integrated_20261020_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75000</v>
+        <v>10550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.28%</t>
+          <t>'+15.68%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
-        <v>197</v>
+        <v>430</v>
       </c>
       <c r="H2" t="n">
-        <v>5.95</v>
+        <v>0.88</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>64500</v>
+        <v>9120</v>
       </c>
       <c r="K2" t="n">
-        <v>68000</v>
+        <v>9500</v>
       </c>
       <c r="L2" t="n">
-        <v>79300</v>
+        <v>11250</v>
       </c>
       <c r="M2" t="n">
-        <v>66700</v>
+        <v>9470</v>
       </c>
       <c r="N2" t="n">
-        <v>5.66</v>
+        <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>126177193400</v>
+        <v>210951104505</v>
       </c>
       <c r="P2" t="n">
-        <v>148300</v>
+        <v>11250</v>
       </c>
       <c r="Q2" t="n">
-        <v>17780</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>72000</v>
+        <v>325000</v>
       </c>
       <c r="S2" t="n">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
+          <t>로봇 및 ESS, 이차전지 사업 연계로 인한 폭등 기대. 신고가 경신 및 조단위 시총 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['소부장', '매출 증가', '저평가 분석']</t>
+          <t>['로봇', 'ESS', '신고가']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10460</v>
+        <v>73700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+14.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>5.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9120</v>
+        <v>64500</v>
       </c>
       <c r="K3" t="n">
-        <v>9500</v>
+        <v>68000</v>
       </c>
       <c r="L3" t="n">
-        <v>11250</v>
+        <v>79300</v>
       </c>
       <c r="M3" t="n">
-        <v>9470</v>
+        <v>66700</v>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>5.66</v>
       </c>
       <c r="O3" t="n">
-        <v>208898239895</v>
+        <v>130619082350</v>
       </c>
       <c r="P3" t="n">
-        <v>11250</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2270</v>
+        <v>17780</v>
       </c>
       <c r="R3" t="n">
-        <v>325000</v>
+        <v>72000</v>
       </c>
       <c r="S3" t="n">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 테마 연계 및 신고가 경신에 따른 급등 기대감. 조단위 시총 및 5배 이상 상승 가능성 제시.</t>
+          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇 테마', '신고가', '조단위 시총']</t>
+          <t>['소부장', '매출 증가', '저평가 분석']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3950</v>
+        <v>3295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.33%</t>
+          <t>'+13.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G4" t="n">
+        <v>173</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2915</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2920</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3365</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2875</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O4" t="n">
+        <v>26085906677</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-45000</v>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>53</v>
-      </c>
-      <c r="F4" t="n">
-        <v>29</v>
-      </c>
-      <c r="G4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>3750</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3770</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4285</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3755</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O4" t="n">
-        <v>40971347991</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6660</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-300000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-8000</v>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
+          <t>김정은 사망설 확산으로 인한 급등 기대. 과거 사망설 당시 대폭등 사례 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['피하주사', '기술 계약', '시장 하락']</t>
+          <t>['김정은 사망설', '급등', '북한']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16910</v>
+        <v>3910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16200</v>
+        <v>3750</v>
       </c>
       <c r="K5" t="n">
-        <v>16500</v>
+        <v>3770</v>
       </c>
       <c r="L5" t="n">
-        <v>18620</v>
+        <v>4285</v>
       </c>
       <c r="M5" t="n">
-        <v>14650</v>
+        <v>3755</v>
       </c>
       <c r="N5" t="n">
-        <v>1.07</v>
+        <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>50554420935</v>
+        <v>41250629941</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>6660</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>2200</v>
       </c>
       <c r="R5" t="n">
-        <v>-2000</v>
+        <v>-300000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 및 빅웨이브와의 주가 차이에 대한 불만 제기. 근거 없는 급등락 반복에 대한 비판.</t>
+          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수', '주가 차이', '근거 부재']</t>
+          <t>['피하주사', '기술 계약', '시장 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42700</v>
+        <v>16080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>905</v>
+        <v>160</v>
       </c>
       <c r="H6" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K6" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L6" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M6" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>11303532900</v>
+        <v>53540417005</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R6" t="n">
-        <v>-21000</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 및 FDA 승인 기대감 속에서 주가 변동성. 매수세 유입 관찰.</t>
+          <t>보호예수 물량 출회 및 주가 하락 우려. 빅웨이브 등 타 종목과의 비교 및 '개잡주' 비판.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '담관암']</t>
+          <t>['보호예수', '주가 하락', '개잡주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19570</v>
+        <v>42450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.71%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="G7" t="n">
-        <v>134</v>
+        <v>934</v>
       </c>
       <c r="H7" t="n">
-        <v>3.07</v>
+        <v>13.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19710</v>
+        <v>42950</v>
       </c>
       <c r="K7" t="n">
-        <v>19450</v>
+        <v>42600</v>
       </c>
       <c r="L7" t="n">
-        <v>21850</v>
+        <v>43200</v>
       </c>
       <c r="M7" t="n">
-        <v>19450</v>
+        <v>41550</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>87566703460</v>
+        <v>11656050700</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>6320</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>-4000</v>
+        <v>-21000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>로봇 섹터와 연관 기대감 및 보안주로서의 역할 언급. 주가 변동성 및 개인 투자자 이탈에 대한 우려.</t>
+          <t>C1 발표 임박 및 바이오 부문 기대. 담관암 FDA 승인 가능성 및 경영진 퇴진 관련 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '변동성']</t>
+          <t>['C1 발표', '담관암', 'FDA 승인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>9592972850</v>
+        <v>9725202325</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211500</v>
+        <v>210750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.98%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="G9" t="n">
-        <v>1480</v>
+        <v>1458</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>1719490994500</v>
+        <v>1781958613500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 논쟁과 정부 정책 비판이 주를 이룸. 주가 관련 직접적인 근거는 부족.</t>
+          <t>정치적 발언으로 인한 하락 우려. 이재명 전 대통령 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '정치 비판', '금융 정책']</t>
+          <t>['이재명', '정치', '하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1220000</v>
+        <v>18880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.46%</t>
+          <t>'-4.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>536</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>1575</v>
+        <v>145</v>
       </c>
       <c r="H10" t="n">
-        <v>48.81</v>
+        <v>3.07</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1277000</v>
+        <v>19710</v>
       </c>
       <c r="K10" t="n">
-        <v>1265000</v>
+        <v>19450</v>
       </c>
       <c r="L10" t="n">
-        <v>1267000</v>
+        <v>21850</v>
       </c>
       <c r="M10" t="n">
-        <v>1183000</v>
+        <v>18460</v>
       </c>
       <c r="N10" t="n">
-        <v>48.82</v>
+        <v>3.32</v>
       </c>
       <c r="O10" t="n">
-        <v>2708070311000</v>
+        <v>91252485800</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>465500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-204000</v>
+        <v>-4000</v>
       </c>
       <c r="S10" t="n">
-        <v>-146000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 우회 상장 반대 청원 및 경영진 비판이 주된 내용. 정치적 이슈와 연계.</t>
+          <t>보안주로서의 기대감과 함께 주가 변동성 언급. 차트 패턴 및 외국인 매수세 주목.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '경영진 비판']</t>
+          <t>['보안주', '차트', '외국인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14270</v>
+        <v>17440</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="H11" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K11" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L11" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M11" t="n">
-        <v>14150</v>
+        <v>17280</v>
       </c>
       <c r="N11" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>17597334830</v>
+        <v>33507155210</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-56000</v>
+        <v>-247000</v>
       </c>
       <c r="S11" t="n">
-        <v>-39000</v>
+        <v>-134000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>실적 개선에도 불구하고 정치적 이슈와 공매도 관련 불만 고조. 주주들의 대차 해지 독려 및 시장 신뢰 하락.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '대차해지']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17450</v>
+        <v>14240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="H12" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,222 +1515,222 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K12" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L12" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M12" t="n">
-        <v>17280</v>
+        <v>14150</v>
       </c>
       <c r="N12" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>32522387830</v>
+        <v>17920982510</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-247000</v>
+        <v>-56000</v>
       </c>
       <c r="S12" t="n">
-        <v>-134000</v>
+        <v>-39000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>3분기 실적 폭증 기대에도 불구하고, 공매도 및 주가 조작 의혹 제기로 인한 부정적 투자 심리. 외인 공매도 비판과 주주들의 대차 해지 촉구가 나타남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['공매도', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2555</v>
+        <v>1215000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.19%</t>
+          <t>'-4.86%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>55</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>532</v>
       </c>
       <c r="G13" t="n">
-        <v>168</v>
+        <v>1577</v>
       </c>
       <c r="H13" t="n">
-        <v>1.14</v>
+        <v>48.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2695</v>
+        <v>1277000</v>
       </c>
       <c r="K13" t="n">
-        <v>2645</v>
+        <v>1265000</v>
       </c>
       <c r="L13" t="n">
-        <v>2715</v>
+        <v>1267000</v>
       </c>
       <c r="M13" t="n">
-        <v>2510</v>
+        <v>1183000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8</v>
+        <v>48.82</v>
       </c>
       <c r="O13" t="n">
-        <v>29335877163</v>
+        <v>2781269977500</v>
       </c>
       <c r="P13" t="n">
-        <v>2755</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>865</v>
+        <v>465500</v>
       </c>
       <c r="R13" t="n">
-        <v>-12000</v>
+        <v>-204000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-146000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
+          <t>자회사 솔리다임 상장 철회 요구. 최태원 회장 및 정치적 요인 관련 부정적 논의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['솔리다임', '최태원', '상장 철회']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31050</v>
+        <v>2530</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.54%</t>
+          <t>'-6.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="H14" t="n">
-        <v>12.79</v>
+        <v>1.14</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>33950</v>
+        <v>2695</v>
       </c>
       <c r="K14" t="n">
-        <v>33250</v>
+        <v>2645</v>
       </c>
       <c r="L14" t="n">
-        <v>34150</v>
+        <v>2715</v>
       </c>
       <c r="M14" t="n">
-        <v>31050</v>
+        <v>2510</v>
       </c>
       <c r="N14" t="n">
-        <v>12.81</v>
+        <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>53651690550</v>
+        <v>29660499883</v>
       </c>
       <c r="P14" t="n">
-        <v>59300</v>
+        <v>2755</v>
       </c>
       <c r="Q14" t="n">
-        <v>22000</v>
+        <v>865</v>
       </c>
       <c r="R14" t="n">
-        <v>-137000</v>
+        <v>-12000</v>
       </c>
       <c r="S14" t="n">
-        <v>-35000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
+          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['태양광', '공매도', '시장 하락']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1587</v>
+        <v>30950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.21%</t>
+          <t>'-8.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>188</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>323</v>
+        <v>201</v>
       </c>
       <c r="H15" t="n">
-        <v>1.77</v>
+        <v>12.79</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1748</v>
+        <v>33950</v>
       </c>
       <c r="K15" t="n">
-        <v>1706</v>
+        <v>33250</v>
       </c>
       <c r="L15" t="n">
-        <v>1895</v>
+        <v>34150</v>
       </c>
       <c r="M15" t="n">
-        <v>1577</v>
+        <v>30800</v>
       </c>
       <c r="N15" t="n">
-        <v>0.83</v>
+        <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>69461254206</v>
+        <v>56675282225</v>
       </c>
       <c r="P15" t="n">
-        <v>2970</v>
+        <v>59300</v>
       </c>
       <c r="Q15" t="n">
-        <v>890</v>
+        <v>22000</v>
       </c>
       <c r="R15" t="n">
-        <v>-457000</v>
+        <v>-137000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-35000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시 기반의 급등세. 2연상 기대감 형성.</t>
+          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '철강 기술력']</t>
+          <t>['태양광', '공매도', '시장 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8680</v>
+        <v>1579</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.70%</t>
+          <t>'-9.67%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="G16" t="n">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9720</v>
+        <v>1748</v>
       </c>
       <c r="K16" t="n">
-        <v>9930</v>
+        <v>1706</v>
       </c>
       <c r="L16" t="n">
-        <v>9930</v>
+        <v>1895</v>
       </c>
       <c r="M16" t="n">
-        <v>8510</v>
+        <v>1571</v>
       </c>
       <c r="N16" t="n">
-        <v>6.15</v>
+        <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>16625101930</v>
+        <v>69822210216</v>
       </c>
       <c r="P16" t="n">
-        <v>14940</v>
+        <v>2970</v>
       </c>
       <c r="Q16" t="n">
-        <v>5390</v>
+        <v>890</v>
       </c>
       <c r="R16" t="n">
-        <v>-273000</v>
+        <v>-457000</v>
       </c>
       <c r="S16" t="n">
-        <v>-244000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주주환원 정책 부재 및 중복상장 우려 제기. 단기적인 주가 변동성에 대한 의구심과 매도 의견 혼재.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등 기대. 우주사업 진출 및 기술력 입증.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '중복상장', '주가 변동성']</t>
+          <t>['스페이스X', '호재 공시', '우주사업']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,178 +1936,178 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7830</v>
+        <v>8640</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-12.42%</t>
+          <t>'-11.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
-        <v>152</v>
+        <v>322</v>
       </c>
       <c r="H17" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K17" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L17" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M17" t="n">
-        <v>7750</v>
+        <v>8510</v>
       </c>
       <c r="N17" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17396819100</v>
+        <v>16797249830</v>
       </c>
       <c r="P17" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q17" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R17" t="n">
-        <v>-36000</v>
+        <v>-273000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>-244000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>주주 환원 부족 및 과거 주가 부진 언급. 중복 상장 이슈 및 공매도 관련 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['주주환원', '중복상장', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71300</v>
+        <v>7830</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.05%</t>
+          <t>'-12.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>702</v>
+        <v>155</v>
       </c>
       <c r="H18" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L18" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M18" t="n">
-        <v>70300</v>
+        <v>7750</v>
       </c>
       <c r="N18" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>96495966100</v>
+        <v>17676138070</v>
       </c>
       <c r="P18" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q18" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R18" t="n">
-        <v>-480000</v>
+        <v>-36000</v>
       </c>
       <c r="S18" t="n">
-        <v>-49000</v>
+        <v>-8000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>공매도 물량 증가 및 주가 급락에 대한 불만 표출. 정치적 이슈와 연관 지어 비판하는 의견 다수.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '주가 급락', '정치적 이슈']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,10 +2115,102 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>71200</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-13.17%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E19" t="n">
+        <v>217</v>
+      </c>
+      <c r="F19" t="n">
+        <v>122</v>
+      </c>
+      <c r="G19" t="n">
+        <v>751</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L19" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M19" t="n">
+        <v>70300</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>98598314300</v>
+      </c>
+      <c r="P19" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-480000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>공매도 비중 증가 및 주가 하락. 정치적 요인 및 이유 없는 하락에 대한 불만.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '정치']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>272210</t>
         </is>

--- a/data/trending_integrated_20261020_13.xlsx
+++ b/data/trending_integrated_20261020_13.xlsx
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10550</v>
+        <v>74100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.68%</t>
+          <t>'+14.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>194</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>430</v>
+        <v>204</v>
       </c>
       <c r="H2" t="n">
-        <v>0.88</v>
+        <v>5.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9120</v>
+        <v>64500</v>
       </c>
       <c r="K2" t="n">
-        <v>9500</v>
+        <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>11250</v>
+        <v>79300</v>
       </c>
       <c r="M2" t="n">
-        <v>9470</v>
+        <v>66700</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>210951104505</v>
+        <v>132959115150</v>
       </c>
       <c r="P2" t="n">
-        <v>11250</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2270</v>
+        <v>17780</v>
       </c>
       <c r="R2" t="n">
-        <v>325000</v>
+        <v>-1000</v>
       </c>
       <c r="S2" t="n">
-        <v>15000</v>
+        <v>118000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 및 ESS, 이차전지 사업 연계로 인한 폭등 기대. 신고가 경신 및 조단위 시총 목표.</t>
+          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '신고가']</t>
+          <t>['소부장', '매출 증가', '저평가 분석']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73700</v>
+        <v>10460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.26%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>455</v>
       </c>
       <c r="H3" t="n">
-        <v>5.95</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>64500</v>
+        <v>9120</v>
       </c>
       <c r="K3" t="n">
-        <v>68000</v>
+        <v>9500</v>
       </c>
       <c r="L3" t="n">
-        <v>79300</v>
+        <v>11250</v>
       </c>
       <c r="M3" t="n">
-        <v>66700</v>
+        <v>9470</v>
       </c>
       <c r="N3" t="n">
-        <v>5.66</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>130619082350</v>
+        <v>212652389345</v>
       </c>
       <c r="P3" t="n">
-        <v>148300</v>
+        <v>11250</v>
       </c>
       <c r="Q3" t="n">
-        <v>17780</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>72000</v>
+        <v>259000</v>
       </c>
       <c r="S3" t="n">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
+          <t>로봇, ESS, 이차전지 관련 복합 테마, 조단위 시총 기대감 및 신고가 경신.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['소부장', '매출 증가', '저평가 분석']</t>
+          <t>['HT로보틱스', '로봇주', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3295</v>
+        <v>3270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.04%</t>
+          <t>'+12.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="H4" t="n">
         <v>0.73</v>
@@ -785,7 +785,7 @@
         <v>2920</v>
       </c>
       <c r="L4" t="n">
-        <v>3365</v>
+        <v>3445</v>
       </c>
       <c r="M4" t="n">
         <v>2875</v>
@@ -794,7 +794,7 @@
         <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>26085906677</v>
+        <v>34760053021</v>
       </c>
       <c r="P4" t="n">
         <v>7050</v>
@@ -803,23 +803,23 @@
         <v>2500</v>
       </c>
       <c r="R4" t="n">
-        <v>-45000</v>
+        <v>-678000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>김정은 사망설 확산으로 인한 급등 기대. 과거 사망설 당시 대폭등 사례 언급.</t>
+          <t>김정은 사망설 관련 지정학적 리스크 부각, 과거 사망설 시 대폭등 사례 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '급등', '북한']</t>
+          <t>['빅텍', '김정은 사망설', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3910</v>
+        <v>3915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+4.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
         <v>1.66</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>41250629941</v>
+        <v>41408627234</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -895,10 +895,10 @@
         <v>2200</v>
       </c>
       <c r="R5" t="n">
-        <v>-300000</v>
+        <v>-136000</v>
       </c>
       <c r="S5" t="n">
-        <v>-8000</v>
+        <v>-18000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16080</v>
+        <v>43000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>964</v>
       </c>
       <c r="H6" t="n">
-        <v>2.03</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16200</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>16500</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>18620</v>
+        <v>43200</v>
       </c>
       <c r="M6" t="n">
-        <v>14650</v>
+        <v>41550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>53540417005</v>
+        <v>12461104500</v>
       </c>
       <c r="P6" t="n">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>14600</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-2000</v>
+        <v>-20000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 및 주가 하락 우려. 빅웨이브 등 타 종목과의 비교 및 '개잡주' 비판.</t>
+          <t>C1 발표 임박 및 바이오 부문 기대. 담관암 FDA 승인 가능성 및 경영진 퇴진 관련 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보호예수', '주가 하락', '개잡주']</t>
+          <t>['C1 발표', '담관암', 'FDA 승인']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42450</v>
+        <v>15870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E7" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>934</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K7" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L7" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M7" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N7" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>11656050700</v>
+        <v>56048086175</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R7" t="n">
-        <v>-21000</v>
+        <v>-52000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C1 발표 임박 및 바이오 부문 기대. 담관암 FDA 승인 가능성 및 경영진 퇴진 관련 논의.</t>
+          <t>보호예수 물량 부담 및 주가 하락에 대한 불만, 개잡주 및 쓰레기 종목 비난.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1 발표', '담관암', 'FDA 승인']</t>
+          <t>['브릴스', '보호예수', '개잡주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7260</v>
+        <v>7280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>9725202325</v>
+        <v>9918871365</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1171,10 +1171,10 @@
         <v>7190</v>
       </c>
       <c r="R8" t="n">
-        <v>-176000</v>
+        <v>-234000</v>
       </c>
       <c r="S8" t="n">
-        <v>-17000</v>
+        <v>-44000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210750</v>
+        <v>211250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G9" t="n">
-        <v>1458</v>
+        <v>1433</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>1781958613500</v>
+        <v>1850135314250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,14 +1263,14 @@
         <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>356000</v>
+        <v>858000</v>
       </c>
       <c r="S9" t="n">
-        <v>-501000</v>
+        <v>-851000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 발언으로 인한 하락 우려. 이재명 전 대통령 관련 부정적 언급.</t>
+          <t>현 정부의 금융 정책 및 경제 상황에 대한 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '정치', '하락']</t>
+          <t>['이재명', '금융정책', '주식 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18880</v>
+        <v>19090</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.21%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.25</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H10" t="n">
         <v>3.07</v>
@@ -1346,7 +1346,7 @@
         <v>3.32</v>
       </c>
       <c r="O10" t="n">
-        <v>91252485800</v>
+        <v>92672992315</v>
       </c>
       <c r="P10" t="n">
         <v>22450</v>
@@ -1355,14 +1355,14 @@
         <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-4000</v>
+        <v>-20000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>보안주로서의 기대감과 함께 주가 변동성 언급. 차트 패턴 및 외국인 매수세 주목.</t>
+          <t>정책 수혜 기대감 있으나 주가 흐름 부진, 개미 무덤 차트 형성 및 설거지 의혹.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', '차트', '외국인']</t>
+          <t>['라온시큐어', '보안주', '정책 수혜']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17440</v>
+        <v>14280</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K11" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L11" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M11" t="n">
-        <v>17280</v>
+        <v>14150</v>
       </c>
       <c r="N11" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>33507155210</v>
+        <v>18384218250</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-247000</v>
+        <v>-89000</v>
       </c>
       <c r="S11" t="n">
-        <v>-134000</v>
+        <v>-44000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>3분기 실적 폭증 기대에도 불구하고, 공매도 및 주가 조작 의혹 제기로 인한 부정적 투자 심리. 외인 공매도 비판과 주주들의 대차 해지 촉구가 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['공매도', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14240</v>
+        <v>17470</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="H12" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K12" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L12" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M12" t="n">
-        <v>14150</v>
+        <v>17280</v>
       </c>
       <c r="N12" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O12" t="n">
-        <v>17920982510</v>
+        <v>34049672310</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-56000</v>
+        <v>-270000</v>
       </c>
       <c r="S12" t="n">
-        <v>-39000</v>
+        <v>-171000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 기대에도 불구하고, 공매도 및 주가 조작 의혹 제기로 인한 부정적 투자 심리. 외인 공매도 비판과 주주들의 대차 해지 촉구가 나타남.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '주가조작']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1215000</v>
+        <v>1218000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-4.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="G13" t="n">
-        <v>1577</v>
+        <v>1586</v>
       </c>
       <c r="H13" t="n">
         <v>48.81</v>
@@ -1622,7 +1622,7 @@
         <v>48.82</v>
       </c>
       <c r="O13" t="n">
-        <v>2781269977500</v>
+        <v>2836098425000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1631,14 +1631,14 @@
         <v>465500</v>
       </c>
       <c r="R13" t="n">
-        <v>-204000</v>
+        <v>-270000</v>
       </c>
       <c r="S13" t="n">
-        <v>-146000</v>
+        <v>-186000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자회사 솔리다임 상장 철회 요구. 최태원 회장 및 정치적 요인 관련 부정적 논의.</t>
+          <t>최태원 회장 및 솔리다임 우회상장 관련 개인투자자 불만 제기, 현 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '상장 철회']</t>
+          <t>['SK하이닉스', '솔리다임', '주주보호']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2530</v>
+        <v>2535</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.12%</t>
+          <t>'-5.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H14" t="n">
         <v>1.14</v>
@@ -1714,7 +1714,7 @@
         <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>29660499883</v>
+        <v>29881196195</v>
       </c>
       <c r="P14" t="n">
         <v>2755</v>
@@ -1723,7 +1723,7 @@
         <v>865</v>
       </c>
       <c r="R14" t="n">
-        <v>-12000</v>
+        <v>57000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30950</v>
+        <v>31100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.84%</t>
+          <t>'-8.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>56675282225</v>
+        <v>57824683850</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1815,10 +1815,10 @@
         <v>22000</v>
       </c>
       <c r="R15" t="n">
-        <v>-137000</v>
+        <v>-365000</v>
       </c>
       <c r="S15" t="n">
-        <v>-35000</v>
+        <v>-64000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.67%</t>
+          <t>'-10.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1892,13 +1892,13 @@
         <v>1895</v>
       </c>
       <c r="M16" t="n">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="N16" t="n">
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>69822210216</v>
+        <v>70096894501</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1907,14 +1907,14 @@
         <v>890</v>
       </c>
       <c r="R16" t="n">
-        <v>-457000</v>
+        <v>-872000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등 기대. 우주사업 진출 및 기술력 입증.</t>
+          <t>스페이스X 관련 호재 공시 및 글로벌 강관 기술력 입증, 코스피 수익률 3위 달성. 2연상 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '우주사업']</t>
+          <t>['KBI동양철관', '스페이스X', '호재공시']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8640</v>
+        <v>8670</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.11%</t>
+          <t>'-10.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>16797249830</v>
+        <v>16893801340</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -1999,14 +1999,14 @@
         <v>5390</v>
       </c>
       <c r="R17" t="n">
-        <v>-273000</v>
+        <v>-187000</v>
       </c>
       <c r="S17" t="n">
-        <v>-244000</v>
+        <v>-530000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주 환원 부족 및 과거 주가 부진 언급. 중복 상장 이슈 및 공매도 관련 우려.</t>
+          <t>과도한 주가 하락 및 주주환원 정책 부재에 대한 불만, 중복상장 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '중복상장', '공매도']</t>
+          <t>['명신산업', '주주환원', '중복상장']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,18 +2039,18 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7830</v>
+        <v>7880</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-12.42%</t>
+          <t>'-11.86%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
@@ -2082,7 +2082,7 @@
         <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>17676138070</v>
+        <v>17817188570</v>
       </c>
       <c r="P18" t="n">
         <v>19150</v>
@@ -2091,10 +2091,10 @@
         <v>3570</v>
       </c>
       <c r="R18" t="n">
-        <v>-36000</v>
+        <v>-72000</v>
       </c>
       <c r="S18" t="n">
-        <v>-8000</v>
+        <v>-33000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71200</v>
+        <v>71300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.17%</t>
+          <t>'-13.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F19" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="H19" t="n">
         <v>9.380000000000001</v>
@@ -2174,7 +2174,7 @@
         <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>98598314300</v>
+        <v>100475138100</v>
       </c>
       <c r="P19" t="n">
         <v>184000</v>
@@ -2183,10 +2183,10 @@
         <v>44750</v>
       </c>
       <c r="R19" t="n">
-        <v>-480000</v>
+        <v>-557000</v>
       </c>
       <c r="S19" t="n">
-        <v>-49000</v>
+        <v>-77000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261020_13.xlsx
+++ b/data/trending_integrated_20261020_13.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74100</v>
+        <v>3415</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.88%</t>
+          <t>'+17.15%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="H2" t="n">
-        <v>5.95</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>64500</v>
+        <v>2915</v>
       </c>
       <c r="K2" t="n">
-        <v>68000</v>
+        <v>2920</v>
       </c>
       <c r="L2" t="n">
-        <v>79300</v>
+        <v>3445</v>
       </c>
       <c r="M2" t="n">
-        <v>66700</v>
+        <v>2875</v>
       </c>
       <c r="N2" t="n">
-        <v>5.66</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>132959115150</v>
+        <v>41426980810</v>
       </c>
       <c r="P2" t="n">
-        <v>148300</v>
+        <v>7050</v>
       </c>
       <c r="Q2" t="n">
-        <v>17780</v>
+        <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>-1000</v>
+        <v>-678000</v>
       </c>
       <c r="S2" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
+          <t>김정은 사망설 확산에 따른 지정학적 리스크 부각 및 급등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['소부장', '매출 증가', '저평가 분석']</t>
+          <t>['김정은', '사망설', '지정학']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10460</v>
+        <v>10510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+15.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" t="n">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>212652389345</v>
+        <v>214910890055</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 관련 복합 테마, 조단위 시총 기대감 및 신고가 경신.</t>
+          <t>로봇, ESS, 이차전지 등 복합 사업에 대한 높은 성장 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['HT로보틱스', '로봇주', '신고가']</t>
+          <t>['로봇', 'ESS', '이차전지']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3270</v>
+        <v>73200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.18%</t>
+          <t>'+13.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H4" t="n">
-        <v>0.73</v>
+        <v>5.95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2915</v>
+        <v>64500</v>
       </c>
       <c r="K4" t="n">
-        <v>2920</v>
+        <v>68000</v>
       </c>
       <c r="L4" t="n">
-        <v>3445</v>
+        <v>79300</v>
       </c>
       <c r="M4" t="n">
-        <v>2875</v>
+        <v>66700</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>5.66</v>
       </c>
       <c r="O4" t="n">
-        <v>34760053021</v>
+        <v>134670701950</v>
       </c>
       <c r="P4" t="n">
-        <v>7050</v>
+        <v>148300</v>
       </c>
       <c r="Q4" t="n">
-        <v>2500</v>
+        <v>17780</v>
       </c>
       <c r="R4" t="n">
-        <v>-678000</v>
+        <v>-1000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 지정학적 리스크 부각, 과거 사망설 시 대폭등 사례 언급.</t>
+          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['빅텍', '김정은 사망설', '지정학적 리스크']</t>
+          <t>['소부장', '매출 증가', '저평가 분석']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3915</v>
+        <v>3975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.40%</t>
+          <t>'+6.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>27</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>41408627234</v>
+        <v>43844130256</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43000</v>
+        <v>42650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>12461104500</v>
+        <v>12912106350</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 임박 및 바이오 부문 기대. 담관암 FDA 승인 가능성 및 경영진 퇴진 관련 논의.</t>
+          <t>C1 발표 임박에 따른 신약 승인 기대감 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1 발표', '담관암', 'FDA 승인']</t>
+          <t>['C1', '신약승인', 'FDA']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15870</v>
+        <v>7260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.96</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="H7" t="n">
-        <v>2.03</v>
+        <v>25.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16200</v>
+        <v>7460</v>
       </c>
       <c r="K7" t="n">
-        <v>16500</v>
+        <v>7410</v>
       </c>
       <c r="L7" t="n">
-        <v>18620</v>
+        <v>7490</v>
       </c>
       <c r="M7" t="n">
-        <v>14650</v>
+        <v>7200</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07</v>
+        <v>25.42</v>
       </c>
       <c r="O7" t="n">
-        <v>56048086175</v>
+        <v>10134760000</v>
       </c>
       <c r="P7" t="n">
-        <v>62100</v>
+        <v>17950</v>
       </c>
       <c r="Q7" t="n">
-        <v>14600</v>
+        <v>7190</v>
       </c>
       <c r="R7" t="n">
-        <v>-52000</v>
+        <v>-234000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-44000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보호예수 물량 부담 및 주가 하락에 대한 불만, 개잡주 및 쓰레기 종목 비난.</t>
+          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['브릴스', '보호예수', '개잡주']</t>
+          <t>['영업이익', '주가 하락', '기술 혁신']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,91 +1103,91 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7280</v>
+        <v>15650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>0.96</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>283</v>
+        <v>205</v>
       </c>
       <c r="H8" t="n">
-        <v>25.4</v>
+        <v>2.03</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7460</v>
+        <v>16200</v>
       </c>
       <c r="K8" t="n">
-        <v>7410</v>
+        <v>16500</v>
       </c>
       <c r="L8" t="n">
-        <v>7490</v>
+        <v>18620</v>
       </c>
       <c r="M8" t="n">
-        <v>7200</v>
+        <v>14650</v>
       </c>
       <c r="N8" t="n">
-        <v>25.42</v>
+        <v>1.07</v>
       </c>
       <c r="O8" t="n">
-        <v>9918871365</v>
+        <v>57295577940</v>
       </c>
       <c r="P8" t="n">
-        <v>17950</v>
+        <v>62100</v>
       </c>
       <c r="Q8" t="n">
-        <v>7190</v>
+        <v>14600</v>
       </c>
       <c r="R8" t="n">
-        <v>-234000</v>
+        <v>-52000</v>
       </c>
       <c r="S8" t="n">
-        <v>-44000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
+          <t>보호예수 물량 출회 및 주가 하락 우려. 잡주 취급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '기술 혁신']</t>
+          <t>['보호예수', '개잡주', '물량']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,95 +1195,95 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211250</v>
+        <v>18980</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.10%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.25</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>527</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>1433</v>
+        <v>158</v>
       </c>
       <c r="H9" t="n">
-        <v>46.04</v>
+        <v>3.07</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>218000</v>
+        <v>19710</v>
       </c>
       <c r="K9" t="n">
-        <v>219500</v>
+        <v>19450</v>
       </c>
       <c r="L9" t="n">
-        <v>219500</v>
+        <v>21850</v>
       </c>
       <c r="M9" t="n">
-        <v>210000</v>
+        <v>18460</v>
       </c>
       <c r="N9" t="n">
-        <v>45.99</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1850135314250</v>
+        <v>93689124925</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>858000</v>
+        <v>-20000</v>
       </c>
       <c r="S9" t="n">
-        <v>-851000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>현 정부의 금융 정책 및 경제 상황에 대한 부정적 언급 다수.</t>
+          <t>로봇 산업 성장과 연계된 보안주로서의 정책적 수혜 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '금융정책', '주식 하락']</t>
+          <t>['보안주', '로봇', '정책']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19090</v>
+        <v>209000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>528</v>
       </c>
       <c r="G10" t="n">
-        <v>151</v>
+        <v>1381</v>
       </c>
       <c r="H10" t="n">
-        <v>3.07</v>
+        <v>46.04</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19710</v>
+        <v>218000</v>
       </c>
       <c r="K10" t="n">
-        <v>19450</v>
+        <v>219500</v>
       </c>
       <c r="L10" t="n">
-        <v>21850</v>
+        <v>219500</v>
       </c>
       <c r="M10" t="n">
-        <v>18460</v>
+        <v>208750</v>
       </c>
       <c r="N10" t="n">
-        <v>3.32</v>
+        <v>45.99</v>
       </c>
       <c r="O10" t="n">
-        <v>92672992315</v>
+        <v>1990866446500</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-20000</v>
+        <v>858000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-851000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정책 수혜 기대감 있으나 주가 흐름 부진, 개미 무덤 차트 형성 및 설거지 의혹.</t>
+          <t>정치인 발언 및 정책 불신으로 인한 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['라온시큐어', '보안주', '정책 수혜']</t>
+          <t>['이재명', '정치', '증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14280</v>
+        <v>14210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'-4.95%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H11" t="n">
         <v>9.779999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>18384218250</v>
+        <v>18808510585</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17470</v>
+        <v>17360</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-5.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.85</v>
       </c>
       <c r="O12" t="n">
-        <v>34049672310</v>
+        <v>35613710210</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>조선업황 부진 및 정치 불확실성으로 인한 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['조선업', '수주', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1218000</v>
+        <v>1210000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-5.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>540</v>
       </c>
       <c r="G13" t="n">
-        <v>1586</v>
+        <v>1663</v>
       </c>
       <c r="H13" t="n">
         <v>48.81</v>
@@ -1622,7 +1622,7 @@
         <v>48.82</v>
       </c>
       <c r="O13" t="n">
-        <v>2836098425000</v>
+        <v>2906854146500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최태원 회장 및 솔리다임 우회상장 관련 개인투자자 불만 제기, 현 정부 정책 비판.</t>
+          <t>솔리다임 우회 상장 반대 청원 및 경영진 불신으로 인한 주가 하락.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '주주보호']</t>
+          <t>['솔리다임', '우회상장', '청원']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-6.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H14" t="n">
         <v>1.14</v>
@@ -1714,7 +1714,7 @@
         <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>29881196195</v>
+        <v>30044943025</v>
       </c>
       <c r="P14" t="n">
         <v>2755</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31100</v>
+        <v>30900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.39%</t>
+          <t>'-8.98%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>57824683850</v>
+        <v>58835858150</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.07%</t>
+          <t>'-10.41%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1892,13 +1892,13 @@
         <v>1895</v>
       </c>
       <c r="M16" t="n">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="N16" t="n">
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>70096894501</v>
+        <v>70663546573</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시 및 글로벌 강관 기술력 입증, 코스피 수익률 3위 달성. 2연상 기대감.</t>
+          <t>스페이스X 납품 계약 체결 기대감에 따른 주가 급등 및 2연상 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['KBI동양철관', '스페이스X', '호재공시']</t>
+          <t>['스페이스X', '철강', '납품']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8670</v>
+        <v>8620</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-10.80%</t>
+          <t>'-11.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>16893801340</v>
+        <v>17071196320</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>과도한 주가 하락 및 주주환원 정책 부재에 대한 불만, 중복상장 우려.</t>
+          <t>주주환원 정책 부재 및 중복 상장 우려 속 단기 상승 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['명신산업', '주주환원', '중복상장']</t>
+          <t>['주주환원', '중복상장', '테슬라']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7880</v>
+        <v>71300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.86%</t>
+          <t>'-13.05%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>224</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="G18" t="n">
-        <v>155</v>
+        <v>772</v>
       </c>
       <c r="H18" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K18" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L18" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M18" t="n">
-        <v>7750</v>
+        <v>70300</v>
       </c>
       <c r="N18" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O18" t="n">
-        <v>17817188570</v>
+        <v>102009979300</v>
       </c>
       <c r="P18" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R18" t="n">
-        <v>-72000</v>
+        <v>-557000</v>
       </c>
       <c r="S18" t="n">
-        <v>-33000</v>
+        <v>-77000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도 비중 증가 및 주가 하락. 정치적 요인 및 이유 없는 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '주가 하락', '정치']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,91 +2115,91 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71300</v>
+        <v>7750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.05%</t>
+          <t>'-13.31%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>219</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>765</v>
+        <v>156</v>
       </c>
       <c r="H19" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L19" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M19" t="n">
-        <v>70300</v>
+        <v>7700</v>
       </c>
       <c r="N19" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O19" t="n">
-        <v>100475138100</v>
+        <v>18490261905</v>
       </c>
       <c r="P19" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q19" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R19" t="n">
-        <v>-557000</v>
+        <v>-72000</v>
       </c>
       <c r="S19" t="n">
-        <v>-77000</v>
+        <v>-33000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>공매도 비중 증가 및 주가 하락. 정치적 요인 및 이유 없는 하락에 대한 불만.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '정치']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_13.xlsx
+++ b/data/trending_integrated_20261020_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3415</v>
+        <v>10540</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.15%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1</v>
+        <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="G2" t="n">
-        <v>231</v>
+        <v>454</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2915</v>
+        <v>9120</v>
       </c>
       <c r="K2" t="n">
-        <v>2920</v>
+        <v>9500</v>
       </c>
       <c r="L2" t="n">
-        <v>3445</v>
+        <v>11250</v>
       </c>
       <c r="M2" t="n">
-        <v>2875</v>
+        <v>9470</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>41426980810</v>
+        <v>216260233280</v>
       </c>
       <c r="P2" t="n">
-        <v>7050</v>
+        <v>11250</v>
       </c>
       <c r="Q2" t="n">
-        <v>2500</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>-678000</v>
+        <v>259000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 사망설 확산에 따른 지정학적 리스크 부각 및 급등 기대.</t>
+          <t>로봇, ESS, 이차전지 등 복합 사업에 대한 높은 성장 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '사망설', '지정학']</t>
+          <t>['로봇', 'ESS', '이차전지']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10510</v>
+        <v>73500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.24%</t>
+          <t>'+13.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="F3" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>453</v>
+        <v>208</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>5.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9120</v>
+        <v>64500</v>
       </c>
       <c r="K3" t="n">
-        <v>9500</v>
+        <v>68000</v>
       </c>
       <c r="L3" t="n">
-        <v>11250</v>
+        <v>79300</v>
       </c>
       <c r="M3" t="n">
-        <v>9470</v>
+        <v>66700</v>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>5.66</v>
       </c>
       <c r="O3" t="n">
-        <v>214910890055</v>
+        <v>136263844750</v>
       </c>
       <c r="P3" t="n">
-        <v>11250</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2270</v>
+        <v>17780</v>
       </c>
       <c r="R3" t="n">
-        <v>259000</v>
+        <v>-1000</v>
       </c>
       <c r="S3" t="n">
-        <v>25000</v>
+        <v>118000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 등 복합 사업에 대한 높은 성장 기대감.</t>
+          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '이차전지']</t>
+          <t>['반도체', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73200</v>
+        <v>3315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.49%</t>
+          <t>'+13.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="H4" t="n">
-        <v>5.95</v>
+        <v>0.73</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>64500</v>
+        <v>2915</v>
       </c>
       <c r="K4" t="n">
-        <v>68000</v>
+        <v>2920</v>
       </c>
       <c r="L4" t="n">
-        <v>79300</v>
+        <v>3445</v>
       </c>
       <c r="M4" t="n">
-        <v>66700</v>
+        <v>2875</v>
       </c>
       <c r="N4" t="n">
-        <v>5.66</v>
+        <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>134670701950</v>
+        <v>45862537125</v>
       </c>
       <c r="P4" t="n">
-        <v>148300</v>
+        <v>7050</v>
       </c>
       <c r="Q4" t="n">
-        <v>17780</v>
+        <v>2500</v>
       </c>
       <c r="R4" t="n">
-        <v>-1000</v>
+        <v>-678000</v>
       </c>
       <c r="S4" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>소부장 매출 증가 기대감 및 저평가 분석 기반 상승세. 목표가 상향 리포트 언급.</t>
+          <t>김정은 사망설 확산에 따른 급등 기대감, 과거 사례 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['소부장', '매출 증가', '저평가 분석']</t>
+          <t>['사망설', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3975</v>
+        <v>3950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.00%</t>
+          <t>'+5.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>43844130256</v>
+        <v>44422358616</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42650</v>
+        <v>42900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>995</v>
+        <v>1009</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>12912106350</v>
+        <v>13308042650</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7260</v>
+        <v>15920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-1.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>0.96</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="H7" t="n">
-        <v>25.4</v>
+        <v>2.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7460</v>
+        <v>16200</v>
       </c>
       <c r="K7" t="n">
-        <v>7410</v>
+        <v>16500</v>
       </c>
       <c r="L7" t="n">
-        <v>7490</v>
+        <v>18620</v>
       </c>
       <c r="M7" t="n">
-        <v>7200</v>
+        <v>14650</v>
       </c>
       <c r="N7" t="n">
-        <v>25.42</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>10134760000</v>
+        <v>58098025010</v>
       </c>
       <c r="P7" t="n">
-        <v>17950</v>
+        <v>62100</v>
       </c>
       <c r="Q7" t="n">
-        <v>7190</v>
+        <v>14600</v>
       </c>
       <c r="R7" t="n">
-        <v>-234000</v>
+        <v>-52000</v>
       </c>
       <c r="S7" t="n">
-        <v>-44000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
+          <t>보호예수 물량 및 개잡주 논란, 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '기술 혁신']</t>
+          <t>['보호예수', '개잡주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,91 +1103,91 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15650</v>
+        <v>7260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.96</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>296</v>
       </c>
       <c r="H8" t="n">
-        <v>2.03</v>
+        <v>25.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16200</v>
+        <v>7460</v>
       </c>
       <c r="K8" t="n">
-        <v>16500</v>
+        <v>7410</v>
       </c>
       <c r="L8" t="n">
-        <v>18620</v>
+        <v>7490</v>
       </c>
       <c r="M8" t="n">
-        <v>14650</v>
+        <v>7200</v>
       </c>
       <c r="N8" t="n">
-        <v>1.07</v>
+        <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>57295577940</v>
+        <v>10309000905</v>
       </c>
       <c r="P8" t="n">
-        <v>62100</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>14600</v>
+        <v>7190</v>
       </c>
       <c r="R8" t="n">
-        <v>-52000</v>
+        <v>-234000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-44000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 및 주가 하락 우려. 잡주 취급.</t>
+          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보호예수', '개잡주', '물량']</t>
+          <t>['영업이익', '주가 하락', '기술 혁신']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18980</v>
+        <v>19020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.25</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H9" t="n">
         <v>3.07</v>
@@ -1254,7 +1254,7 @@
         <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>93689124925</v>
+        <v>94063712935</v>
       </c>
       <c r="P9" t="n">
         <v>22450</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 산업 성장과 연계된 보안주로서의 정책적 수혜 기대.</t>
+          <t>보안주로서의 역할 부각, 2만원 안착 여부 및 외국인 매수세 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '정책']</t>
+          <t>['보안주', '외국인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209000</v>
+        <v>210250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="G10" t="n">
-        <v>1381</v>
+        <v>1351</v>
       </c>
       <c r="H10" t="n">
         <v>46.04</v>
@@ -1346,7 +1346,7 @@
         <v>45.99</v>
       </c>
       <c r="O10" t="n">
-        <v>1990866446500</v>
+        <v>2108836324000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치인 발언 및 정책 불신으로 인한 주가 하락 우려.</t>
+          <t>정치적 발언 및 비난에 치우친 게시글 다수, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['이재명', '정치', '증시']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14210</v>
+        <v>1216000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.95%</t>
+          <t>'-4.78%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>551</v>
       </c>
       <c r="G11" t="n">
-        <v>166</v>
+        <v>1660</v>
       </c>
       <c r="H11" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14950</v>
+        <v>1277000</v>
       </c>
       <c r="K11" t="n">
-        <v>14610</v>
+        <v>1265000</v>
       </c>
       <c r="L11" t="n">
-        <v>14940</v>
+        <v>1267000</v>
       </c>
       <c r="M11" t="n">
-        <v>14150</v>
+        <v>1183000</v>
       </c>
       <c r="N11" t="n">
-        <v>9.699999999999999</v>
+        <v>48.82</v>
       </c>
       <c r="O11" t="n">
-        <v>18808510585</v>
+        <v>2963410556000</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>465500</v>
       </c>
       <c r="R11" t="n">
-        <v>-89000</v>
+        <v>-270000</v>
       </c>
       <c r="S11" t="n">
-        <v>-44000</v>
+        <v>-186000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 기대에도 불구하고, 공매도 및 주가 조작 의혹 제기로 인한 부정적 투자 심리. 외인 공매도 비판과 주주들의 대차 해지 촉구가 나타남.</t>
+          <t>자회사 솔리다임 우회상장 반대 국민청원 다수, 경영진 및 정치권 비난.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '주가조작']</t>
+          <t>['우회상장', '국민청원']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17360</v>
+        <v>14210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.14%</t>
+          <t>'-4.95%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="H12" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K12" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L12" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M12" t="n">
-        <v>17280</v>
+        <v>14150</v>
       </c>
       <c r="N12" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>35613710210</v>
+        <v>19175277435</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-270000</v>
+        <v>-89000</v>
       </c>
       <c r="S12" t="n">
-        <v>-171000</v>
+        <v>-44000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선업황 부진 및 정치 불확실성으로 인한 주가 하락 전망.</t>
+          <t>정치적 발언 및 공매도 비난, 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업', '수주', '주가']</t>
+          <t>['공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1210000</v>
+        <v>17390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.25%</t>
+          <t>'-4.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>540</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>1663</v>
+        <v>223</v>
       </c>
       <c r="H13" t="n">
-        <v>48.81</v>
+        <v>27.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1277000</v>
+        <v>18300</v>
       </c>
       <c r="K13" t="n">
-        <v>1265000</v>
+        <v>18140</v>
       </c>
       <c r="L13" t="n">
-        <v>1267000</v>
+        <v>18140</v>
       </c>
       <c r="M13" t="n">
-        <v>1183000</v>
+        <v>17280</v>
       </c>
       <c r="N13" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="O13" t="n">
-        <v>2906854146500</v>
+        <v>36863740100</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R13" t="n">
         <v>-270000</v>
       </c>
       <c r="S13" t="n">
-        <v>-186000</v>
+        <v>-171000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>솔리다임 우회 상장 반대 청원 및 경영진 불신으로 인한 주가 하락.</t>
+          <t>조선업황 부진 및 정치 불확실성으로 인한 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '청원']</t>
+          <t>['조선업', '수주', '주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H14" t="n">
         <v>1.14</v>
@@ -1714,7 +1714,7 @@
         <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>30044943025</v>
+        <v>30233402225</v>
       </c>
       <c r="P14" t="n">
         <v>2755</v>
@@ -1774,13 +1774,13 @@
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1800,13 +1800,13 @@
         <v>34150</v>
       </c>
       <c r="M15" t="n">
-        <v>30800</v>
+        <v>30750</v>
       </c>
       <c r="N15" t="n">
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>58835858150</v>
+        <v>60645284075</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.41%</t>
+          <t>'-10.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G16" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1892,13 +1892,13 @@
         <v>1895</v>
       </c>
       <c r="M16" t="n">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="N16" t="n">
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>70663546573</v>
+        <v>71156210549</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8620</v>
+        <v>8610</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.32%</t>
+          <t>'-11.42%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17071196320</v>
+        <v>17169243920</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주환원 정책 부재 및 중복 상장 우려 속 단기 상승 기대감.</t>
+          <t>주가 하락 및 급등락에 대한 혼란, 주주환원 정책 부재 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '중복상장', '테슬라']</t>
+          <t>['주주환원']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71300</v>
+        <v>71100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.05%</t>
+          <t>'-13.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F18" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G18" t="n">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="H18" t="n">
         <v>9.380000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>9.44</v>
       </c>
       <c r="O18" t="n">
-        <v>102009979300</v>
+        <v>103929293350</v>
       </c>
       <c r="P18" t="n">
         <v>184000</v>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7750</v>
+        <v>7730</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.31%</t>
+          <t>'-13.53%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
         <v>156</v>
@@ -2168,13 +2168,13 @@
         <v>9010</v>
       </c>
       <c r="M19" t="n">
-        <v>7700</v>
+        <v>7650</v>
       </c>
       <c r="N19" t="n">
         <v>36.39</v>
       </c>
       <c r="O19" t="n">
-        <v>18490261905</v>
+        <v>18976789285</v>
       </c>
       <c r="P19" t="n">
         <v>19150</v>

--- a/data/trending_integrated_20261020_13.xlsx
+++ b/data/trending_integrated_20261020_13.xlsx
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10540</v>
+        <v>73000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.57%</t>
+          <t>'+13.18%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>454</v>
+        <v>210</v>
       </c>
       <c r="H2" t="n">
-        <v>0.88</v>
+        <v>5.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9120</v>
+        <v>64500</v>
       </c>
       <c r="K2" t="n">
-        <v>9500</v>
+        <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>11250</v>
+        <v>79300</v>
       </c>
       <c r="M2" t="n">
-        <v>9470</v>
+        <v>66700</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>216260233280</v>
+        <v>138921832250</v>
       </c>
       <c r="P2" t="n">
-        <v>11250</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2270</v>
+        <v>17780</v>
       </c>
       <c r="R2" t="n">
-        <v>259000</v>
+        <v>-1000</v>
       </c>
       <c r="S2" t="n">
-        <v>25000</v>
+        <v>118000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 등 복합 사업에 대한 높은 성장 기대감.</t>
+          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '이차전지']</t>
+          <t>['반도체', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73500</v>
+        <v>10280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.95%</t>
+          <t>'+12.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="G3" t="n">
-        <v>208</v>
+        <v>453</v>
       </c>
       <c r="H3" t="n">
-        <v>5.95</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>64500</v>
+        <v>9120</v>
       </c>
       <c r="K3" t="n">
-        <v>68000</v>
+        <v>9500</v>
       </c>
       <c r="L3" t="n">
-        <v>79300</v>
+        <v>11250</v>
       </c>
       <c r="M3" t="n">
-        <v>66700</v>
+        <v>9470</v>
       </c>
       <c r="N3" t="n">
-        <v>5.66</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>136263844750</v>
+        <v>218920850220</v>
       </c>
       <c r="P3" t="n">
-        <v>148300</v>
+        <v>11250</v>
       </c>
       <c r="Q3" t="n">
-        <v>17780</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>-1000</v>
+        <v>259000</v>
       </c>
       <c r="S3" t="n">
-        <v>118000</v>
+        <v>25000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
+          <t>HT로보틱스 주가 급등 및 로봇주 상승 추세에 대한 긍정적 전망. 신고가 경신 및 조단위 시총 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '실적', '목표가']</t>
+          <t>['로봇주', '신고가', '매수세']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3315</v>
+        <v>3275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.72%</t>
+          <t>'+12.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F4" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="H4" t="n">
         <v>0.73</v>
@@ -794,7 +794,7 @@
         <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>45862537125</v>
+        <v>48882115077</v>
       </c>
       <c r="P4" t="n">
         <v>7050</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>김정은 사망설 확산에 따른 급등 기대감, 과거 사례 언급.</t>
+          <t>김정은 사망설 확산에 따른 빅텍 주가 급등. 과거 사망설 시점의 급등 사례 언급 및 기대감 고조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['사망설', '급등']</t>
+          <t>['김정은사망설', '급등', '북한']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3950</v>
+        <v>3997</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.33%</t>
+          <t>'+6.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>44422358616</v>
+        <v>44799650811</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42900</v>
+        <v>42850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G6" t="n">
-        <v>1009</v>
+        <v>1024</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>13308042650</v>
+        <v>13633246350</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 임박에 따른 신약 승인 기대감 및 주가 상승 전망.</t>
+          <t>HLB의 C1 발표 및 담관암 FDA 승인 가능성에 대한 기대감. 클래스 1 확신 및 100만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1', '신약승인', 'FDA']</t>
+          <t>['C1발표', 'FDA승인', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15920</v>
+        <v>7260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.73%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.96</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="H7" t="n">
-        <v>2.03</v>
+        <v>25.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16200</v>
+        <v>7460</v>
       </c>
       <c r="K7" t="n">
-        <v>16500</v>
+        <v>7410</v>
       </c>
       <c r="L7" t="n">
-        <v>18620</v>
+        <v>7490</v>
       </c>
       <c r="M7" t="n">
-        <v>14650</v>
+        <v>7200</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07</v>
+        <v>25.42</v>
       </c>
       <c r="O7" t="n">
-        <v>58098025010</v>
+        <v>10511342685</v>
       </c>
       <c r="P7" t="n">
-        <v>62100</v>
+        <v>17950</v>
       </c>
       <c r="Q7" t="n">
-        <v>14600</v>
+        <v>7190</v>
       </c>
       <c r="R7" t="n">
-        <v>-52000</v>
+        <v>-234000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-44000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보호예수 물량 및 개잡주 논란, 주가 하락 우려.</t>
+          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보호예수', '개잡주']</t>
+          <t>['영업이익', '주가 하락', '기술 혁신']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7260</v>
+        <v>210000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>545</v>
       </c>
       <c r="G8" t="n">
-        <v>296</v>
+        <v>1435</v>
       </c>
       <c r="H8" t="n">
-        <v>25.4</v>
+        <v>46.04</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7460</v>
+        <v>217000</v>
       </c>
       <c r="K8" t="n">
-        <v>7410</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7490</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>25.42</v>
+        <v>45.99</v>
       </c>
       <c r="O8" t="n">
-        <v>10309000905</v>
+        <v>2166888000000</v>
       </c>
       <c r="P8" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7190</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-234000</v>
+        <v>858000</v>
       </c>
       <c r="S8" t="n">
-        <v>-44000</v>
+        <v>-851000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
+          <t>이재명 정부 정책 실패 및 한국 증시 저평가에 대한 불만 표출. 삼성전자 주가 하락에 대한 정치적 책임론 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,51 +1187,51 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '기술 혁신']</t>
+          <t>['정치', '증시', '저평가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19020</v>
+        <v>15660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.25</v>
+        <v>0.96</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="H9" t="n">
-        <v>3.07</v>
+        <v>2.03</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19710</v>
+        <v>16200</v>
       </c>
       <c r="K9" t="n">
-        <v>19450</v>
+        <v>16500</v>
       </c>
       <c r="L9" t="n">
-        <v>21850</v>
+        <v>18620</v>
       </c>
       <c r="M9" t="n">
-        <v>18460</v>
+        <v>14650</v>
       </c>
       <c r="N9" t="n">
-        <v>3.32</v>
+        <v>1.07</v>
       </c>
       <c r="O9" t="n">
-        <v>94063712935</v>
+        <v>58559179480</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>62100</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>14600</v>
       </c>
       <c r="R9" t="n">
-        <v>-20000</v>
+        <v>-52000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안주로서의 역할 부각, 2만원 안착 여부 및 외국인 매수세 주목.</t>
+          <t>브릴스 주가 급락 및 보호예수 물량 출회 우려. 개잡주 및 쓰레기 종목으로 분류하며 부정적 평가.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '외국인']</t>
+          <t>['보호예수', '개잡주', '주가하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210250</v>
+        <v>18980</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.25</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>104</v>
       </c>
       <c r="F10" t="n">
-        <v>552</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>1351</v>
+        <v>164</v>
       </c>
       <c r="H10" t="n">
-        <v>46.04</v>
+        <v>3.07</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>218000</v>
+        <v>19710</v>
       </c>
       <c r="K10" t="n">
-        <v>219500</v>
+        <v>19450</v>
       </c>
       <c r="L10" t="n">
-        <v>219500</v>
+        <v>21850</v>
       </c>
       <c r="M10" t="n">
-        <v>208750</v>
+        <v>18460</v>
       </c>
       <c r="N10" t="n">
-        <v>45.99</v>
+        <v>3.32</v>
       </c>
       <c r="O10" t="n">
-        <v>2108836324000</v>
+        <v>94912542785</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>858000</v>
+        <v>-20000</v>
       </c>
       <c r="S10" t="n">
-        <v>-851000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 발언 및 비난에 치우친 게시글 다수, 주가 하락에 대한 불만 표출.</t>
+          <t>라온시큐어 보안주로서의 중요성 부각 및 주가 상승 기대. 2만원 안착 여부 및 외국인 매수세 주목.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['보안주', '정책', '외국인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1216000</v>
+        <v>1214000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.78%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="G11" t="n">
-        <v>1660</v>
+        <v>1781</v>
       </c>
       <c r="H11" t="n">
         <v>48.81</v>
@@ -1438,7 +1438,7 @@
         <v>48.82</v>
       </c>
       <c r="O11" t="n">
-        <v>2963410556000</v>
+        <v>3012827907500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자회사 솔리다임 우회상장 반대 국민청원 다수, 경영진 및 정치권 비난.</t>
+          <t>SK하이닉스 주가 하락에 대한 최태원 회장 및 정부 정책 비판. 솔리다임 우회 상장 반대 청원.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['우회상장', '국민청원']</t>
+          <t>['솔리다임', '우회상장', '최태원']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14210</v>
+        <v>14200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.95%</t>
+          <t>'-5.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H12" t="n">
         <v>9.779999999999999</v>
@@ -1530,7 +1530,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>19175277435</v>
+        <v>19708674335</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 발언 및 공매도 비난, 주가 조작 의혹 제기.</t>
+          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17390</v>
+        <v>17360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.97%</t>
+          <t>'-5.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
         <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="H13" t="n">
         <v>27.78</v>
@@ -1622,7 +1622,7 @@
         <v>27.85</v>
       </c>
       <c r="O13" t="n">
-        <v>36863740100</v>
+        <v>38322268050</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조선업황 부진 및 정치 불확실성으로 인한 주가 하락 전망.</t>
+          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선업', '수주', '주가']</t>
+          <t>['조선업', '정부정책', '수주']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2530</v>
+        <v>2540</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.12%</t>
+          <t>'-5.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H14" t="n">
         <v>1.14</v>
@@ -1714,7 +1714,7 @@
         <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>30233402225</v>
+        <v>30404236999</v>
       </c>
       <c r="P14" t="n">
         <v>2755</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30900</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.98%</t>
+          <t>'-9.43%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1800,13 +1800,13 @@
         <v>34150</v>
       </c>
       <c r="M15" t="n">
-        <v>30750</v>
+        <v>30650</v>
       </c>
       <c r="N15" t="n">
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>60645284075</v>
+        <v>62047984400</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1568</v>
+        <v>1577</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.30%</t>
+          <t>'-9.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>101</v>
       </c>
       <c r="G16" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>71156210549</v>
+        <v>71275809454</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8610</v>
+        <v>8590</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.42%</t>
+          <t>'-11.63%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17169243920</v>
+        <v>17254228690</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락 및 급등락에 대한 혼란, 주주환원 정책 부재 비판.</t>
+          <t>명신산업 주가 하락에 대한 불만 표출. 주주환원 정책 부재 및 과거 주가 흐름에 대한 지적. 중복 상장 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원']</t>
+          <t>['주주환원', '중복상장', '테슬라']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71100</v>
+        <v>70700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.29%</t>
+          <t>'-13.78%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F18" t="n">
         <v>128</v>
       </c>
       <c r="G18" t="n">
-        <v>785</v>
+        <v>817</v>
       </c>
       <c r="H18" t="n">
         <v>9.380000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>9.44</v>
       </c>
       <c r="O18" t="n">
-        <v>103929293350</v>
+        <v>106647769850</v>
       </c>
       <c r="P18" t="n">
         <v>184000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>공매도 비중 증가 및 주가 하락. 정치적 요인 및 이유 없는 하락에 대한 불만.</t>
+          <t>한화시스템 주가 급락에 대한 공매도 및 정부 정책 비판. 이유 없는 하락에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '정치']</t>
+          <t>['공매도', '정부정책', '주가하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7730</v>
+        <v>7690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.53%</t>
+          <t>'-13.98%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H19" t="n">
         <v>36.01</v>
@@ -2168,13 +2168,13 @@
         <v>9010</v>
       </c>
       <c r="M19" t="n">
-        <v>7650</v>
+        <v>7640</v>
       </c>
       <c r="N19" t="n">
         <v>36.39</v>
       </c>
       <c r="O19" t="n">
-        <v>18976789285</v>
+        <v>19337292510</v>
       </c>
       <c r="P19" t="n">
         <v>19150</v>
